--- a/prepis_app/firmy.xlsx
+++ b/prepis_app/firmy.xlsx
@@ -471,7 +471,6 @@
           <t>25101</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,7 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heršpická 788 9, Brno</t>
+          <t>Heršpická 788/9, Brno</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -494,7 +493,6 @@
           <t>63900</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,7 +507,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cacovická 1592 30, Brno</t>
+          <t>Cacovická 1592/30, Brno</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -517,7 +515,6 @@
           <t>61400</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -532,7 +529,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Budějovická 1912 64, Praha</t>
+          <t>Budějovická 1912/64, Praha</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -540,7 +537,6 @@
           <t>14000</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -563,7 +559,6 @@
           <t>25101</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -578,7 +573,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hvězdova 1716 2, Praha</t>
+          <t>Hvězdova 1716/2, Praha</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -586,7 +581,6 @@
           <t>14000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/prepis_app/firmy.xlsx
+++ b/prepis_app/firmy.xlsx
@@ -1,34 +1,148 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="630" yWindow="630" windowWidth="37095" windowHeight="19350"/>
   </bookViews>
   <sheets>
-    <sheet name="Firmy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Firmy" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+  <si>
+    <t>Název</t>
+  </si>
+  <si>
+    <t>IČO</t>
+  </si>
+  <si>
+    <t>Adresa</t>
+  </si>
+  <si>
+    <t>PSČ</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Albion Cars s.r.o.</t>
+  </si>
+  <si>
+    <t>04168313</t>
+  </si>
+  <si>
+    <t>K Chotobuzi 333, Čestlice</t>
+  </si>
+  <si>
+    <t>25101</t>
+  </si>
+  <si>
+    <t>AUTO CARDION s. r. o.</t>
+  </si>
+  <si>
+    <t>04156854</t>
+  </si>
+  <si>
+    <t>Heršpická 788/9, Brno</t>
+  </si>
+  <si>
+    <t>63900</t>
+  </si>
+  <si>
+    <t>EV trans s.r.o.</t>
+  </si>
+  <si>
+    <t>06583539</t>
+  </si>
+  <si>
+    <t>Cacovická 1592/30, Brno</t>
+  </si>
+  <si>
+    <t>61400</t>
+  </si>
+  <si>
+    <t>JE &amp; NE, spol. s r.o.</t>
+  </si>
+  <si>
+    <t>44960263</t>
+  </si>
+  <si>
+    <t>Branka 506/36, Brno</t>
+  </si>
+  <si>
+    <t>62400</t>
+  </si>
+  <si>
+    <t>Leasing České spořitelny, a.s.</t>
+  </si>
+  <si>
+    <t>27089444</t>
+  </si>
+  <si>
+    <t>Budějovická 1912/64, Praha</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>MONETA Auto, s.r.o.</t>
+  </si>
+  <si>
+    <t>60112743</t>
+  </si>
+  <si>
+    <t>Vyskočilova 1442/1, Praha</t>
+  </si>
+  <si>
+    <t>ORBION CARS s.r.o.</t>
+  </si>
+  <si>
+    <t>21231800</t>
+  </si>
+  <si>
+    <t>Raiffeisen - Leasing, s.r.o.</t>
+  </si>
+  <si>
+    <t>61467863</t>
+  </si>
+  <si>
+    <t>Hvězdova 1716/2, Praha</t>
+  </si>
+  <si>
+    <t>ŠkoFIN s.r.o.</t>
+  </si>
+  <si>
+    <t>45805369</t>
+  </si>
+  <si>
+    <t>Pekařská 635/6, Praha</t>
+  </si>
+  <si>
+    <t>15500</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +161,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,178 +460,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Název</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>IČO</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Adresa</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>PSČ</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Albion Cars s.r.o.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>04168313</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>K Chotobuzi 333, Čestlice</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AUTO CARDION s. r. o.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>04156854</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Heršpická 788/9, Brno</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>63900</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EV trans s.r.o.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>06583539</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cacovická 1592/30, Brno</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>61400</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Leasing České spořitelny, a.s.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>27089444</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Budějovická 1912/64, Praha</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>14000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ORBION CARS s.r.o.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>21231800</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>K Chotobuzi 333, Čestlice</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>25101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Raiffeisen - Leasing, s.r.o.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>61467863</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Hvězdova 1716/2, Praha</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>14000</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>1496696121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>1384218354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
